--- a/projects/04-columnar-query-engine/spreadsheets/04_columnar-query-engine_features.xlsx
+++ b/projects/04-columnar-query-engine/spreadsheets/04_columnar-query-engine_features.xlsx
@@ -1882,7 +1882,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -11012,7 +11012,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -11282,7 +11282,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -11417,7 +11417,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -11552,7 +11552,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -11867,7 +11867,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -12137,7 +12137,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -12227,7 +12227,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -12497,7 +12497,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -13172,7 +13172,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -13262,7 +13262,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -13397,7 +13397,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -13442,7 +13442,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -13487,7 +13487,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -13532,7 +13532,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -14252,7 +14252,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -14432,7 +14432,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -15422,7 +15422,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -15692,7 +15692,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -15737,7 +15737,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -15782,7 +15782,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -16383,7 +16383,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Specified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
